--- a/CritPath_GanttChart_Template_v1.3.xlsx
+++ b/CritPath_GanttChart_Template_v1.3.xlsx
@@ -3,9 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5293F12B-3712-415E-9156-59601D8FDF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhiji\projects\excel-gantt-critical-path\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B313486F-2E19-4A35-B303-61F1C3634DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{8DC6E374-7269-49C6-81EA-7974F74BE503}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8DC6E374-7269-49C6-81EA-7974F74BE503}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
@@ -2084,14 +2089,14 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3578,22 +3583,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:90" s="13" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="str">
+      <c r="A1" s="77" t="str">
         <f ca="1">IF(OR(ISERROR($Q$2),ISERROR($CL$2)),"ERROR: inspect Python cells; do not use cached schedule outputs.",IF(COUNTIF($CL$3:$CL$1037,"?*")&gt;0,"WARNING: fixed-date conflicts. Review column CL. Float ignores fixed dates.","No constraint conflicts detected. Float ignores fixed dates. See README."))</f>
         <v>No constraint conflicts detected. Float ignores fixed dates. See README.</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
       <c r="N1" s="12"/>
       <c r="Q1" s="14"/>
       <c r="R1" s="14"/>
@@ -32448,7 +32453,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="76" t="s">
         <v>187</v>
       </c>
     </row>
